--- a/aec/results/신촌/multivariable_results.xlsx
+++ b/aec/results/신촌/multivariable_results.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case_비교_요약" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case1_linear_coef" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case1_logistic_coef" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case1_linear_summary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case1_logistic_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case2_linear_coef" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case2_logistic_coef" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case2_linear_summary" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case2_logistic_summary" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case3_linear_coef" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case3_logistic_coef" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case3_linear_summary" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case3_logistic_summary" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Case_비교_요약" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Case1_linear_coef" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Case1_logistic_coef" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Case1_linear_summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Case1_logistic_summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Case2_linear_coef" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Case2_logistic_coef" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Case2_linear_summary" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Case2_logistic_summary" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Case3_linear_coef" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Case3_logistic_coef" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Case3_linear_summary" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Case3_logistic_summary" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2477,7 +2477,7 @@
         <v>11.7509</v>
       </c>
       <c r="C2" t="n">
-        <v>126868.4674</v>
+        <v>126868.466</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -2895,7 +2895,7 @@
         <v>121.0235</v>
       </c>
       <c r="C21" t="n">
-        <v>3.629552230970935e+52</v>
+        <v>3.629551954709278e+52</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
@@ -3203,7 +3203,7 @@
         <v>136.4841</v>
       </c>
       <c r="C35" t="n">
-        <v>1.880610302180746e+59</v>
+        <v>1.880610138473604e+59</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
@@ -3467,7 +3467,7 @@
         <v>130.2981</v>
       </c>
       <c r="C47" t="n">
-        <v>3.870378678550905e+56</v>
+        <v>3.87037835553249e+56</v>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
@@ -3577,7 +3577,7 @@
         <v>120.0481</v>
       </c>
       <c r="C52" t="n">
-        <v>1.368410520058814e+52</v>
+        <v>1.368410416321512e+52</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
@@ -3599,7 +3599,7 @@
         <v>106.3247</v>
       </c>
       <c r="C53" t="n">
-        <v>1.500434572365682e+46</v>
+        <v>1.500434470303972e+46</v>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
@@ -3643,7 +3643,7 @@
         <v>205.8957</v>
       </c>
       <c r="C55" t="n">
-        <v>2.626468543852966e+89</v>
+        <v>2.626468207671853e+89</v>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>

--- a/aec/results/신촌/multivariable_results.xlsx
+++ b/aec/results/신촌/multivariable_results.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Case_비교_요약" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Case1_linear_coef" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Case1_logistic_coef" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Case1_linear_summary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Case1_logistic_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Case2_linear_coef" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Case2_logistic_coef" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Case2_linear_summary" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Case2_logistic_summary" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Case3_linear_coef" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Case3_logistic_coef" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Case3_linear_summary" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Case3_logistic_summary" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case_비교_요약" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case1_linear_coef" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case1_logistic_coef" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case1_linear_summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case1_logistic_summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case2_linear_coef" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case2_logistic_coef" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case2_linear_summary" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case2_logistic_summary" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case3_linear_coef" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case3_logistic_coef" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case3_linear_summary" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Case3_logistic_summary" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1297</v>
+        <v>1265</v>
       </c>
       <c r="C3" t="n">
-        <v>1297</v>
+        <v>1265</v>
       </c>
       <c r="D3" t="n">
-        <v>1297</v>
+        <v>1265</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -506,13 +506,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5183</v>
+        <v>0.5139</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5455</v>
+        <v>0.5437</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5814</v>
+        <v>0.584</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -527,13 +527,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.5132</v>
       </c>
       <c r="C5" t="n">
-        <v>0.543</v>
+        <v>0.5411</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5636</v>
+        <v>0.5661</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -549,17 +549,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5.6777e-206</t>
+          <t>1.9777e-198</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.3924e-215</t>
+          <t>4.7165e-209</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.1680e-196</t>
+          <t>9.4353e-193</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -575,13 +575,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21.4418</v>
+        <v>21.5585</v>
       </c>
       <c r="C7" t="n">
-        <v>20.8283</v>
+        <v>20.8889</v>
       </c>
       <c r="D7" t="n">
-        <v>19.9873</v>
+        <v>19.9457</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -596,13 +596,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15.8795</v>
+        <v>15.9654</v>
       </c>
       <c r="C8" t="n">
-        <v>15.4551</v>
+        <v>15.4942</v>
       </c>
       <c r="D8" t="n">
-        <v>14.6877</v>
+        <v>14.6597</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11638.23</v>
+        <v>11364.96</v>
       </c>
       <c r="C9" t="n">
-        <v>11572.92</v>
+        <v>11295.14</v>
       </c>
       <c r="D9" t="n">
-        <v>11558.01</v>
+        <v>11268.24</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -638,13 +638,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11653.73</v>
+        <v>11380.39</v>
       </c>
       <c r="C10" t="n">
-        <v>11614.27</v>
+        <v>11336.28</v>
       </c>
       <c r="D10" t="n">
-        <v>11837.08</v>
+        <v>11540.81</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -670,13 +670,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1297</v>
+        <v>1265</v>
       </c>
       <c r="C12" t="n">
-        <v>1297</v>
+        <v>1265</v>
       </c>
       <c r="D12" t="n">
-        <v>1297</v>
+        <v>1265</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="C13" t="n">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="D13" t="n">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -712,13 +712,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.614</v>
+        <v>0.6146</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6546</v>
+        <v>0.655</v>
       </c>
       <c r="D14" t="n">
-        <v>0.718</v>
+        <v>0.7221</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5737</v>
+        <v>0.5783</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6192</v>
+        <v>0.6211</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6868</v>
+        <v>0.6881</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -754,13 +754,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6526</v>
+        <v>0.6522</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6893</v>
+        <v>0.6911</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7494</v>
+        <v>0.7531</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -776,17 +776,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.2160e-03</t>
+          <t>1.5210e-03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.7660e-01</t>
+          <t>9.0313e-02</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6.1556e-01</t>
+          <t>6.0767e-01</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.0314</v>
+        <v>0.0321</v>
       </c>
       <c r="C19" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1713</v>
+        <v>0.1755</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1806</v>
+        <v>0.1816</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1748</v>
+        <v>0.1754</v>
       </c>
       <c r="D20" t="n">
-        <v>0.162</v>
+        <v>0.1625</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1425.39</v>
+        <v>1396.11</v>
       </c>
       <c r="C21" t="n">
-        <v>1395.6</v>
+        <v>1364.37</v>
       </c>
       <c r="D21" t="n">
-        <v>1396.34</v>
+        <v>1364.49</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -888,13 +888,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1440.9</v>
+        <v>1411.54</v>
       </c>
       <c r="C22" t="n">
-        <v>1436.95</v>
+        <v>1405.51</v>
       </c>
       <c r="D22" t="n">
-        <v>1675.4</v>
+        <v>1637.06</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -960,23 +960,23 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>93.8464</v>
+        <v>94.0565</v>
       </c>
       <c r="C2" t="n">
-        <v>53.7777</v>
+        <v>54.0572</v>
       </c>
       <c r="D2" t="n">
-        <v>133.9151</v>
+        <v>134.0559</v>
       </c>
       <c r="E2" t="n">
-        <v>20.4237</v>
+        <v>20.3878</v>
       </c>
       <c r="F2" t="n">
-        <v>4.595</v>
+        <v>4.6134</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4.7685e-06</t>
+          <t>4.3826e-06</t>
         </is>
       </c>
     </row>
@@ -987,23 +987,23 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42.464</v>
+        <v>42.0604</v>
       </c>
       <c r="C3" t="n">
-        <v>40.1201</v>
+        <v>39.692</v>
       </c>
       <c r="D3" t="n">
-        <v>44.808</v>
+        <v>44.4287</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1948</v>
+        <v>1.2072</v>
       </c>
       <c r="F3" t="n">
-        <v>35.5422</v>
+        <v>34.8422</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.6734e-191</t>
+          <t>7.4351e-185</t>
         </is>
       </c>
     </row>
@@ -1014,23 +1014,23 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-4.4207</v>
+        <v>-4.6031</v>
       </c>
       <c r="C4" t="n">
-        <v>-5.6094</v>
+        <v>-5.7954</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.232</v>
+        <v>-3.4107</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6059</v>
+        <v>0.6077</v>
       </c>
       <c r="F4" t="n">
-        <v>-7.2959</v>
+        <v>-7.574</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>5.2698e-13</t>
+          <t>7.1516e-14</t>
         </is>
       </c>
     </row>
@@ -1041,23 +1041,23 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-8.3621</v>
+        <v>-12.6516</v>
       </c>
       <c r="C5" t="n">
-        <v>-17.3972</v>
+        <v>-22.2665</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6729000000000001</v>
+        <v>-3.0368</v>
       </c>
       <c r="E5" t="n">
-        <v>4.6053</v>
+        <v>4.9007</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.8158</v>
+        <v>-2.5816</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6.9648e-02</t>
+          <t>9.9514e-03</t>
         </is>
       </c>
     </row>
@@ -1068,23 +1068,23 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-2.8807</v>
+        <v>-3.6768</v>
       </c>
       <c r="C6" t="n">
-        <v>-4.7753</v>
+        <v>-5.6132</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9861</v>
+        <v>-1.7404</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9657</v>
+        <v>0.987</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.983</v>
+        <v>-3.7253</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.9096e-03</t>
+          <t>2.0410e-04</t>
         </is>
       </c>
     </row>
@@ -1095,23 +1095,23 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.4917</v>
+        <v>1.3528</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0835</v>
+        <v>-0.0585</v>
       </c>
       <c r="D7" t="n">
-        <v>2.8999</v>
+        <v>2.764</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7178</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0782</v>
+        <v>1.8807</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.7894e-02</t>
+          <t>6.0258e-02</t>
         </is>
       </c>
     </row>
@@ -1122,23 +1122,23 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.4559</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.7165</v>
+        <v>-0.8545</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8466</v>
+        <v>1.7664</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6532</v>
+        <v>0.6679</v>
       </c>
       <c r="F8" t="n">
-        <v>0.865</v>
+        <v>0.6826</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3.8722e-01</t>
+          <t>4.9498e-01</t>
         </is>
       </c>
     </row>
@@ -1149,23 +1149,23 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14.6558</v>
+        <v>19.0328</v>
       </c>
       <c r="C9" t="n">
-        <v>5.9013</v>
+        <v>9.6714</v>
       </c>
       <c r="D9" t="n">
-        <v>23.4103</v>
+        <v>28.3942</v>
       </c>
       <c r="E9" t="n">
-        <v>4.4623</v>
+        <v>4.7715</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2844</v>
+        <v>3.9888</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.0506e-03</t>
+          <t>7.0377e-05</t>
         </is>
       </c>
     </row>
@@ -1176,23 +1176,23 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27.6128</v>
+        <v>28.1679</v>
       </c>
       <c r="C10" t="n">
-        <v>-21.535</v>
+        <v>-20.889</v>
       </c>
       <c r="D10" t="n">
-        <v>76.7606</v>
+        <v>77.22490000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>25.0514</v>
+        <v>25.0045</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1022</v>
+        <v>1.1265</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.7057e-01</t>
+          <t>2.6017e-01</t>
         </is>
       </c>
     </row>
@@ -1203,23 +1203,23 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11.5943</v>
+        <v>13.3509</v>
       </c>
       <c r="C11" t="n">
-        <v>-29.9361</v>
+        <v>-28.3212</v>
       </c>
       <c r="D11" t="n">
-        <v>53.1248</v>
+        <v>55.023</v>
       </c>
       <c r="E11" t="n">
-        <v>21.1688</v>
+        <v>21.2404</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5477</v>
+        <v>0.6286</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>5.8399e-01</t>
+          <t>5.2976e-01</t>
         </is>
       </c>
     </row>
@@ -1230,23 +1230,23 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24.9115</v>
+        <v>24.3304</v>
       </c>
       <c r="C12" t="n">
-        <v>-31.7991</v>
+        <v>-32.2852</v>
       </c>
       <c r="D12" t="n">
-        <v>81.622</v>
+        <v>80.946</v>
       </c>
       <c r="E12" t="n">
-        <v>28.9063</v>
+        <v>28.8572</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8618</v>
+        <v>0.8431</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3.8896e-01</t>
+          <t>3.9932e-01</t>
         </is>
       </c>
     </row>
@@ -1257,23 +1257,23 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26.0656</v>
+        <v>26.4072</v>
       </c>
       <c r="C13" t="n">
-        <v>-15.6502</v>
+        <v>-15.2313</v>
       </c>
       <c r="D13" t="n">
-        <v>67.7814</v>
+        <v>68.0457</v>
       </c>
       <c r="E13" t="n">
-        <v>21.2632</v>
+        <v>21.2233</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2259</v>
+        <v>1.2443</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.2049e-01</t>
+          <t>2.1365e-01</t>
         </is>
       </c>
     </row>
@@ -1284,23 +1284,23 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13.9427</v>
+        <v>14.5463</v>
       </c>
       <c r="C14" t="n">
-        <v>-29.3639</v>
+        <v>-28.6789</v>
       </c>
       <c r="D14" t="n">
-        <v>57.2493</v>
+        <v>57.7714</v>
       </c>
       <c r="E14" t="n">
-        <v>22.0741</v>
+        <v>22.032</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.6602</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>5.2774e-01</t>
+          <t>5.0923e-01</t>
         </is>
       </c>
     </row>
@@ -1311,23 +1311,23 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>33.8231</v>
+        <v>32.9587</v>
       </c>
       <c r="C15" t="n">
-        <v>-15.4045</v>
+        <v>-16.1999</v>
       </c>
       <c r="D15" t="n">
-        <v>83.05070000000001</v>
+        <v>82.1173</v>
       </c>
       <c r="E15" t="n">
-        <v>25.0921</v>
+        <v>25.0563</v>
       </c>
       <c r="F15" t="n">
-        <v>1.348</v>
+        <v>1.3154</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1.7792e-01</t>
+          <t>1.8863e-01</t>
         </is>
       </c>
     </row>
@@ -1338,23 +1338,23 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14.562</v>
+        <v>13.6122</v>
       </c>
       <c r="C16" t="n">
-        <v>-42.1283</v>
+        <v>-42.9758</v>
       </c>
       <c r="D16" t="n">
-        <v>71.25239999999999</v>
+        <v>70.2002</v>
       </c>
       <c r="E16" t="n">
-        <v>28.896</v>
+        <v>28.8431</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5039</v>
+        <v>0.4719</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>6.1439e-01</t>
+          <t>6.3705e-01</t>
         </is>
       </c>
     </row>
@@ -1365,23 +1365,23 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9.0937</v>
+        <v>8.6311</v>
       </c>
       <c r="C17" t="n">
-        <v>-32.4501</v>
+        <v>-32.9467</v>
       </c>
       <c r="D17" t="n">
-        <v>50.6375</v>
+        <v>50.2089</v>
       </c>
       <c r="E17" t="n">
-        <v>21.1756</v>
+        <v>21.1924</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4294</v>
+        <v>0.4073</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6.6768e-01</t>
+          <t>6.8388e-01</t>
         </is>
       </c>
     </row>
@@ -1392,23 +1392,23 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31.5863</v>
+        <v>31.8979</v>
       </c>
       <c r="C18" t="n">
-        <v>-17.5743</v>
+        <v>-17.1764</v>
       </c>
       <c r="D18" t="n">
-        <v>80.7469</v>
+        <v>80.9722</v>
       </c>
       <c r="E18" t="n">
-        <v>25.058</v>
+        <v>25.0134</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2605</v>
+        <v>1.2752</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.0772e-01</t>
+          <t>2.0247e-01</t>
         </is>
       </c>
     </row>
@@ -1419,23 +1419,23 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17.5198</v>
+        <v>17.1131</v>
       </c>
       <c r="C19" t="n">
-        <v>-39.1722</v>
+        <v>-39.4854</v>
       </c>
       <c r="D19" t="n">
-        <v>74.2118</v>
+        <v>73.7116</v>
       </c>
       <c r="E19" t="n">
-        <v>28.8969</v>
+        <v>28.8485</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6063</v>
+        <v>0.5931999999999999</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>5.4443e-01</t>
+          <t>5.5315e-01</t>
         </is>
       </c>
     </row>
@@ -1446,23 +1446,23 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9.209300000000001</v>
+        <v>13.9447</v>
       </c>
       <c r="C20" t="n">
-        <v>-31.541</v>
+        <v>-27.0064</v>
       </c>
       <c r="D20" t="n">
-        <v>49.9597</v>
+        <v>54.8959</v>
       </c>
       <c r="E20" t="n">
-        <v>20.7711</v>
+        <v>20.873</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4434</v>
+        <v>0.6681</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>6.5757e-01</t>
+          <t>5.0421e-01</t>
         </is>
       </c>
     </row>
@@ -1473,23 +1473,23 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-20.3334</v>
+        <v>-20.3696</v>
       </c>
       <c r="C21" t="n">
-        <v>-77.0834</v>
+        <v>-77.03570000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>36.4165</v>
+        <v>36.2965</v>
       </c>
       <c r="E21" t="n">
-        <v>28.9264</v>
+        <v>28.8829</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7029</v>
+        <v>-0.7052</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4.8223e-01</t>
+          <t>4.8079e-01</t>
         </is>
       </c>
     </row>
@@ -1500,23 +1500,23 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>20.1721</v>
+        <v>19.5279</v>
       </c>
       <c r="C22" t="n">
-        <v>-36.6348</v>
+        <v>-37.2459</v>
       </c>
       <c r="D22" t="n">
-        <v>76.979</v>
+        <v>76.3018</v>
       </c>
       <c r="E22" t="n">
-        <v>28.9554</v>
+        <v>28.9379</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6967</v>
+        <v>0.6748</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4.8615e-01</t>
+          <t>4.9992e-01</t>
         </is>
       </c>
     </row>
@@ -1527,23 +1527,23 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32.749</v>
+        <v>34.6706</v>
       </c>
       <c r="C23" t="n">
-        <v>-24.0463</v>
+        <v>-22.0236</v>
       </c>
       <c r="D23" t="n">
-        <v>89.5442</v>
+        <v>91.3648</v>
       </c>
       <c r="E23" t="n">
-        <v>28.9495</v>
+        <v>28.8973</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1312</v>
+        <v>1.1998</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2.5817e-01</t>
+          <t>2.3046e-01</t>
         </is>
       </c>
     </row>
@@ -1554,23 +1554,23 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>67.223</v>
+        <v>68.2469</v>
       </c>
       <c r="C24" t="n">
-        <v>10.3333</v>
+        <v>11.3802</v>
       </c>
       <c r="D24" t="n">
-        <v>124.1126</v>
+        <v>125.1136</v>
       </c>
       <c r="E24" t="n">
-        <v>28.9976</v>
+        <v>28.9852</v>
       </c>
       <c r="F24" t="n">
-        <v>2.3182</v>
+        <v>2.3545</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.0599e-02</t>
+          <t>1.8704e-02</t>
         </is>
       </c>
     </row>
@@ -1581,23 +1581,23 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>15.0469</v>
+        <v>14.7059</v>
       </c>
       <c r="C25" t="n">
-        <v>-28.3288</v>
+        <v>-28.5932</v>
       </c>
       <c r="D25" t="n">
-        <v>58.4227</v>
+        <v>58.0051</v>
       </c>
       <c r="E25" t="n">
-        <v>22.1094</v>
+        <v>22.0697</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6806</v>
+        <v>0.6663</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>4.9627e-01</t>
+          <t>5.0532e-01</t>
         </is>
       </c>
     </row>
@@ -1608,23 +1608,23 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-13.8553</v>
+        <v>-14.5181</v>
       </c>
       <c r="C26" t="n">
-        <v>-60.2159</v>
+        <v>-60.8016</v>
       </c>
       <c r="D26" t="n">
-        <v>32.5053</v>
+        <v>31.7655</v>
       </c>
       <c r="E26" t="n">
-        <v>23.6308</v>
+        <v>23.5909</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.5863</v>
+        <v>-0.6153999999999999</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>5.5776e-01</t>
+          <t>5.3840e-01</t>
         </is>
       </c>
     </row>
@@ -1635,23 +1635,23 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.6286</v>
+        <v>7.0426</v>
       </c>
       <c r="C27" t="n">
-        <v>-38.6932</v>
+        <v>-39.1961</v>
       </c>
       <c r="D27" t="n">
-        <v>53.9503</v>
+        <v>53.2813</v>
       </c>
       <c r="E27" t="n">
-        <v>23.611</v>
+        <v>23.5681</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3231</v>
+        <v>0.2988</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>7.4668e-01</t>
+          <t>7.6513e-01</t>
         </is>
       </c>
     </row>
@@ -1662,23 +1662,23 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7.689</v>
+        <v>7.7202</v>
       </c>
       <c r="C28" t="n">
-        <v>-35.1827</v>
+        <v>-35.0746</v>
       </c>
       <c r="D28" t="n">
-        <v>50.5608</v>
+        <v>50.515</v>
       </c>
       <c r="E28" t="n">
-        <v>21.8525</v>
+        <v>21.8127</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3519</v>
+        <v>0.3539</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>7.2500e-01</t>
+          <t>7.2345e-01</t>
         </is>
       </c>
     </row>
@@ -1689,725 +1689,698 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.798</v>
+        <v>-0.1185</v>
       </c>
       <c r="C29" t="n">
-        <v>-37.6623</v>
+        <v>-40.5521</v>
       </c>
       <c r="D29" t="n">
-        <v>43.2584</v>
+        <v>40.3151</v>
       </c>
       <c r="E29" t="n">
-        <v>20.6233</v>
+        <v>20.6092</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1357</v>
+        <v>-0.0057</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>8.9210e-01</t>
+          <t>9.9541e-01</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Model_LightSpeed16</t>
+          <t>Model_MX 16</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7.0881</v>
+        <v>6.0456</v>
       </c>
       <c r="C30" t="n">
-        <v>-49.7655</v>
+        <v>-50.5767</v>
       </c>
       <c r="D30" t="n">
-        <v>63.9417</v>
+        <v>62.6678</v>
       </c>
       <c r="E30" t="n">
-        <v>28.9792</v>
+        <v>28.8606</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2446</v>
+        <v>0.2095</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>8.0681e-01</t>
+          <t>8.3411e-01</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Model_MX 16</t>
+          <t>Model_Optima CT660</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>6.0363</v>
+        <v>14.0481</v>
       </c>
       <c r="C31" t="n">
-        <v>-50.6935</v>
+        <v>-29.7253</v>
       </c>
       <c r="D31" t="n">
-        <v>62.7661</v>
+        <v>57.8216</v>
       </c>
       <c r="E31" t="n">
-        <v>28.9161</v>
+        <v>22.3115</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2088</v>
+        <v>0.6296</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>8.3468e-01</t>
+          <t>5.2905e-01</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Model_Optima CT660</t>
+          <t>Model_Revolution CT</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>12.1257</v>
+        <v>4.8961</v>
       </c>
       <c r="C32" t="n">
-        <v>-31.1644</v>
+        <v>-36.1407</v>
       </c>
       <c r="D32" t="n">
-        <v>55.4159</v>
+        <v>45.933</v>
       </c>
       <c r="E32" t="n">
-        <v>22.0657</v>
+        <v>20.9166</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5495</v>
+        <v>0.2341</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>5.8274e-01</t>
+          <t>8.1496e-01</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Model_Revolution CT</t>
+          <t>Model_Revolution EVO</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5.39</v>
+        <v>-2.5822</v>
       </c>
       <c r="C33" t="n">
-        <v>-35.7108</v>
+        <v>-42.8809</v>
       </c>
       <c r="D33" t="n">
-        <v>46.4907</v>
+        <v>37.7165</v>
       </c>
       <c r="E33" t="n">
-        <v>20.9497</v>
+        <v>20.5404</v>
       </c>
       <c r="F33" t="n">
-        <v>0.2573</v>
+        <v>-0.1257</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>7.9700e-01</t>
+          <t>8.9998e-01</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Model_Revolution EVO</t>
+          <t>Model_Revolution Frontier</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.9149</v>
+        <v>-27.5225</v>
       </c>
       <c r="C34" t="n">
-        <v>-42.2763</v>
+        <v>-84.1765</v>
       </c>
       <c r="D34" t="n">
-        <v>38.4465</v>
+        <v>29.1314</v>
       </c>
       <c r="E34" t="n">
-        <v>20.5729</v>
+        <v>28.8768</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.0931</v>
+        <v>-0.9530999999999999</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>9.2586e-01</t>
+          <t>3.4073e-01</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Model_Revolution Frontier</t>
+          <t>Model_Revolution HD</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-27.6398</v>
+        <v>9.8079</v>
       </c>
       <c r="C35" t="n">
-        <v>-84.3844</v>
+        <v>-46.787</v>
       </c>
       <c r="D35" t="n">
-        <v>29.1048</v>
+        <v>66.4028</v>
       </c>
       <c r="E35" t="n">
-        <v>28.9237</v>
+        <v>28.8466</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.9556</v>
+        <v>0.34</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>3.3945e-01</t>
+          <t>7.3391e-01</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Model_Revolution HD</t>
+          <t>Model_SOMATOM Definition</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>9.3949</v>
+        <v>12.11</v>
       </c>
       <c r="C36" t="n">
-        <v>-47.307</v>
+        <v>-37.0349</v>
       </c>
       <c r="D36" t="n">
-        <v>66.0968</v>
+        <v>61.2548</v>
       </c>
       <c r="E36" t="n">
-        <v>28.9019</v>
+        <v>25.0493</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3251</v>
+        <v>0.4834</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>7.4519e-01</t>
+          <t>6.2887e-01</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition</t>
+          <t>Model_SOMATOM Definition AS</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>13.3491</v>
+        <v>17.7004</v>
       </c>
       <c r="C37" t="n">
-        <v>-35.8727</v>
+        <v>-31.4733</v>
       </c>
       <c r="D37" t="n">
-        <v>62.5709</v>
+        <v>66.8741</v>
       </c>
       <c r="E37" t="n">
-        <v>25.0892</v>
+        <v>25.064</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5321</v>
+        <v>0.7062</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>5.9478e-01</t>
+          <t>4.8020e-01</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition AS</t>
+          <t>Model_SOMATOM Definition AS+</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>16.866</v>
+        <v>9.9321</v>
       </c>
       <c r="C38" t="n">
-        <v>-32.3915</v>
+        <v>-30.2237</v>
       </c>
       <c r="D38" t="n">
-        <v>66.12350000000001</v>
+        <v>50.0878</v>
       </c>
       <c r="E38" t="n">
-        <v>25.1074</v>
+        <v>20.4676</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6718</v>
+        <v>0.4853</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>5.0187e-01</t>
+          <t>6.2758e-01</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition AS+</t>
+          <t>Model_SOMATOM Definition Edge</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10.283</v>
+        <v>17.7918</v>
       </c>
       <c r="C39" t="n">
-        <v>-29.9342</v>
+        <v>-26.1272</v>
       </c>
       <c r="D39" t="n">
-        <v>50.5001</v>
+        <v>61.7107</v>
       </c>
       <c r="E39" t="n">
-        <v>20.4994</v>
+        <v>22.3856</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5016</v>
+        <v>0.7948</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>6.1602e-01</t>
+          <t>4.2689e-01</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition Edge</t>
+          <t>Model_SOMATOM Definition Flash</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>18.3193</v>
+        <v>13.404</v>
       </c>
       <c r="C40" t="n">
-        <v>-25.6717</v>
+        <v>-26.7026</v>
       </c>
       <c r="D40" t="n">
-        <v>62.3102</v>
+        <v>53.5107</v>
       </c>
       <c r="E40" t="n">
-        <v>22.4229</v>
+        <v>20.4425</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>4.1409e-01</t>
+          <t>5.1215e-01</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition Flash</t>
+          <t>Model_SOMATOM Drive</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>13.4756</v>
+        <v>26.4174</v>
       </c>
       <c r="C41" t="n">
-        <v>-26.6968</v>
+        <v>-30.1334</v>
       </c>
       <c r="D41" t="n">
-        <v>53.6481</v>
+        <v>82.9682</v>
       </c>
       <c r="E41" t="n">
-        <v>20.4766</v>
+        <v>28.8242</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6581</v>
+        <v>0.9165</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>5.1060e-01</t>
+          <t>3.5959e-01</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Drive</t>
+          <t>Model_SOMATOM Emotion 16</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26.2153</v>
+        <v>34.3823</v>
       </c>
       <c r="C42" t="n">
-        <v>-30.4434</v>
+        <v>-22.2421</v>
       </c>
       <c r="D42" t="n">
-        <v>82.874</v>
+        <v>91.0067</v>
       </c>
       <c r="E42" t="n">
-        <v>28.8799</v>
+        <v>28.8617</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9077</v>
+        <v>1.1913</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>3.6419e-01</t>
+          <t>2.3378e-01</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Emotion 16</t>
+          <t>Model_SOMATOM Force</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>33.8313</v>
+        <v>18.5364</v>
       </c>
       <c r="C43" t="n">
-        <v>-22.8994</v>
+        <v>-21.6069</v>
       </c>
       <c r="D43" t="n">
-        <v>90.562</v>
+        <v>58.6797</v>
       </c>
       <c r="E43" t="n">
-        <v>28.9166</v>
+        <v>20.4612</v>
       </c>
       <c r="F43" t="n">
-        <v>1.17</v>
+        <v>0.9059</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2.4224e-01</t>
+          <t>3.6515e-01</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Force</t>
+          <t>Model_SOMATOM Perspective</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>18.2883</v>
+        <v>10.4689</v>
       </c>
       <c r="C44" t="n">
-        <v>-21.9261</v>
+        <v>-32.3001</v>
       </c>
       <c r="D44" t="n">
-        <v>58.5026</v>
+        <v>53.2379</v>
       </c>
       <c r="E44" t="n">
-        <v>20.4979</v>
+        <v>21.7995</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8922</v>
+        <v>0.4802</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>3.7246e-01</t>
+          <t>6.3115e-01</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Perspective</t>
+          <t>Model_SOMATOM Scope</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>10.2163</v>
+        <v>16.1939</v>
       </c>
       <c r="C45" t="n">
-        <v>-32.6306</v>
+        <v>-30.0131</v>
       </c>
       <c r="D45" t="n">
-        <v>53.0632</v>
+        <v>62.4008</v>
       </c>
       <c r="E45" t="n">
-        <v>21.8398</v>
+        <v>23.5519</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4678</v>
+        <v>0.6876</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>6.4002e-01</t>
+          <t>4.9185e-01</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Scope</t>
+          <t>Model_SOMATOM go.Top</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>15.672</v>
+        <v>-4.1877</v>
       </c>
       <c r="C46" t="n">
-        <v>-30.622</v>
+        <v>-61.1032</v>
       </c>
       <c r="D46" t="n">
-        <v>61.966</v>
+        <v>52.7277</v>
       </c>
       <c r="E46" t="n">
-        <v>23.5968</v>
+        <v>29.01</v>
       </c>
       <c r="F46" t="n">
-        <v>0.6642</v>
+        <v>-0.1444</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>5.0671e-01</t>
+          <t>8.8524e-01</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Model_SOMATOM go.Top</t>
+          <t>Model_Scope</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>-5.1436</v>
+        <v>25.0103</v>
       </c>
       <c r="C47" t="n">
-        <v>-62.0923</v>
+        <v>-31.5753</v>
       </c>
       <c r="D47" t="n">
-        <v>51.8051</v>
+        <v>81.5959</v>
       </c>
       <c r="E47" t="n">
-        <v>29.0277</v>
+        <v>28.8419</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.1772</v>
+        <v>0.8672</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>8.5938e-01</t>
+          <t>3.8603e-01</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Model_Scope</t>
+          <t>Model_Sensation 16</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>24.0459</v>
+        <v>42.1122</v>
       </c>
       <c r="C48" t="n">
-        <v>-32.6459</v>
+        <v>-14.4521</v>
       </c>
       <c r="D48" t="n">
-        <v>80.7376</v>
+        <v>98.6765</v>
       </c>
       <c r="E48" t="n">
-        <v>28.8967</v>
+        <v>28.831</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8321</v>
+        <v>1.4607</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>4.0549e-01</t>
+          <t>1.4437e-01</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Model_Sensation 16</t>
+          <t>Model_Sensation 64</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>42.1782</v>
+        <v>5.3938</v>
       </c>
       <c r="C49" t="n">
-        <v>-14.4934</v>
+        <v>-34.9556</v>
       </c>
       <c r="D49" t="n">
-        <v>98.8497</v>
+        <v>45.7431</v>
       </c>
       <c r="E49" t="n">
-        <v>28.8864</v>
+        <v>20.5662</v>
       </c>
       <c r="F49" t="n">
-        <v>1.4601</v>
+        <v>0.2623</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1.4451e-01</t>
+          <t>7.9316e-01</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Model_Sensation 64</t>
+          <t>Model_Sensation Open</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>5.7396</v>
+        <v>27.0033</v>
       </c>
       <c r="C50" t="n">
-        <v>-34.6799</v>
+        <v>-16.9372</v>
       </c>
       <c r="D50" t="n">
-        <v>46.1591</v>
+        <v>70.94370000000001</v>
       </c>
       <c r="E50" t="n">
-        <v>20.6025</v>
+        <v>22.3966</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2786</v>
+        <v>1.2057</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>7.8061e-01</t>
+          <t>2.2817e-01</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Model_Sensation Open</t>
+          <t>Model_Spirit</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>26.3187</v>
+        <v>-0.2857</v>
       </c>
       <c r="C51" t="n">
-        <v>-17.6755</v>
+        <v>-56.9127</v>
       </c>
       <c r="D51" t="n">
-        <v>70.3128</v>
+        <v>56.3412</v>
       </c>
       <c r="E51" t="n">
-        <v>22.4245</v>
+        <v>28.863</v>
       </c>
       <c r="F51" t="n">
-        <v>1.1737</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2.4076e-01</t>
+          <t>9.9210e-01</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Model_Spirit</t>
+          <t>Model_Supria</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-1.0344</v>
+        <v>3.6443</v>
       </c>
       <c r="C52" t="n">
-        <v>-57.7668</v>
+        <v>-53.1504</v>
       </c>
       <c r="D52" t="n">
-        <v>55.698</v>
+        <v>60.4389</v>
       </c>
       <c r="E52" t="n">
-        <v>28.9175</v>
+        <v>28.9485</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.0358</v>
+        <v>0.1259</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>9.7147e-01</t>
+          <t>8.9984e-01</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Model_Supria</t>
+          <t>Model_iCT 256</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6846</v>
+        <v>10.2599</v>
       </c>
       <c r="C53" t="n">
-        <v>-56.1953</v>
+        <v>-29.8333</v>
       </c>
       <c r="D53" t="n">
-        <v>57.5645</v>
+        <v>50.353</v>
       </c>
       <c r="E53" t="n">
-        <v>28.9926</v>
+        <v>20.4357</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0236</v>
+        <v>0.5021</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>9.8117e-01</t>
+          <t>6.1572e-01</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Model_iCT 256</t>
+          <t>Model_iCT SP</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10.6156</v>
+        <v>-30.0625</v>
       </c>
       <c r="C54" t="n">
-        <v>-29.5439</v>
+        <v>-86.7127</v>
       </c>
       <c r="D54" t="n">
-        <v>50.7751</v>
+        <v>26.5877</v>
       </c>
       <c r="E54" t="n">
-        <v>20.47</v>
+        <v>28.8748</v>
       </c>
       <c r="F54" t="n">
-        <v>0.5185999999999999</v>
+        <v>-1.0411</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>6.0414e-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Model_iCT SP</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>-29.3183</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-86.0736</v>
-      </c>
-      <c r="D55" t="n">
-        <v>27.437</v>
-      </c>
-      <c r="E55" t="n">
-        <v>28.9291</v>
-      </c>
-      <c r="F55" t="n">
-        <v>-1.0135</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>3.1104e-01</t>
+          <t>2.9802e-01</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2474,10 +2447,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.7509</v>
+        <v>8.9108</v>
       </c>
       <c r="C2" t="n">
-        <v>126868.466</v>
+        <v>7411.3487</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
@@ -2496,10 +2469,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1551</v>
+        <v>0.1489</v>
       </c>
       <c r="C3" t="n">
-        <v>1.1677</v>
+        <v>1.1606</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
@@ -2518,10 +2491,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4235</v>
+        <v>0.4272</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5273</v>
+        <v>1.5329</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -2540,10 +2513,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8444</v>
+        <v>0.9794</v>
       </c>
       <c r="C5" t="n">
-        <v>2.3265</v>
+        <v>2.6629</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -2562,10 +2535,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2678</v>
+        <v>0.3017</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3071</v>
+        <v>1.3522</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -2584,10 +2557,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.1134</v>
+        <v>-0.1432</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8928</v>
+        <v>0.8665</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -2606,10 +2579,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5223</v>
+        <v>0.5446</v>
       </c>
       <c r="C8" t="n">
-        <v>1.6859</v>
+        <v>1.724</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
@@ -2628,10 +2601,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1.6562</v>
+        <v>-1.7924</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1909</v>
+        <v>0.1666</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -2650,7 +2623,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-94.7333</v>
+        <v>-81.6677</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -2672,7 +2645,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-13.3437</v>
+        <v>-10.4092</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -2694,7 +2667,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-48.0595</v>
+        <v>-39.9416</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -2716,7 +2689,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-196.7057</v>
+        <v>-168.5773</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -2738,7 +2711,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-13.5405</v>
+        <v>-10.7408</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -2760,7 +2733,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-63.0547</v>
+        <v>-52.0151</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -2782,7 +2755,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-32.213</v>
+        <v>-26.5489</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -2804,10 +2777,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-12.3117</v>
+        <v>-9.401199999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
@@ -2826,7 +2799,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-79.74550000000001</v>
+        <v>-69.7624</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -2848,7 +2821,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-49.3882</v>
+        <v>-41.1846</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -2870,7 +2843,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-12.1815</v>
+        <v>-9.972</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -2892,10 +2865,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>121.0235</v>
+        <v>105.3565</v>
       </c>
       <c r="C21" t="n">
-        <v>3.629551954709278e+52</v>
+        <v>5.698362895386974e+45</v>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
@@ -2914,7 +2887,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-62.5225</v>
+        <v>-49.4268</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -2936,7 +2909,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-92.6157</v>
+        <v>-82.8691</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -2958,7 +2931,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-17.0043</v>
+        <v>-17.2414</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -2980,7 +2953,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-91.3698</v>
+        <v>-77.714</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -3002,10 +2975,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-11.2473</v>
+        <v>-8.3691</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
@@ -3024,7 +2997,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-72.9802</v>
+        <v>-62.3162</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -3046,7 +3019,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-13.3397</v>
+        <v>-10.5004</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -3068,10 +3041,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-12.3941</v>
+        <v>-9.369</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
@@ -3086,11 +3059,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Model_LightSpeed16</t>
+          <t>Model_MX 16</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-24.8986</v>
+        <v>-25.0115</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -3108,11 +3081,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Model_MX 16</t>
+          <t>Model_Optima CT660</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-29.0098</v>
+        <v>-150.7856</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -3130,14 +3103,14 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Model_Optima CT660</t>
+          <t>Model_Revolution CT</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-189.6884</v>
+        <v>-9.6699</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
@@ -3152,14 +3125,14 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Model_Revolution CT</t>
+          <t>Model_Revolution EVO</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-12.565</v>
+        <v>-8.9626</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
@@ -3174,14 +3147,14 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Model_Revolution EVO</t>
+          <t>Model_Revolution Frontier</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-11.8201</v>
+        <v>117.6051</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>1.189168026865881e+51</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
@@ -3196,14 +3169,14 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Model_Revolution Frontier</t>
+          <t>Model_Revolution HD</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>136.4841</v>
+        <v>-46.0376</v>
       </c>
       <c r="C35" t="n">
-        <v>1.880610138473604e+59</v>
+        <v>0</v>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
@@ -3218,11 +3191,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Model_Revolution HD</t>
+          <t>Model_SOMATOM Definition</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-52.6682</v>
+        <v>-43.812</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -3240,11 +3213,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition</t>
+          <t>Model_SOMATOM Definition AS</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-52.4581</v>
+        <v>-60.6388</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -3262,11 +3235,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition AS</t>
+          <t>Model_SOMATOM Definition AS+</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-68.2931</v>
+        <v>-10.0363</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -3284,11 +3257,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition AS+</t>
+          <t>Model_SOMATOM Definition Edge</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-12.9269</v>
+        <v>-10.2901</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -3306,11 +3279,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition Edge</t>
+          <t>Model_SOMATOM Definition Flash</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-13.1767</v>
+        <v>-10.3451</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
@@ -3328,11 +3301,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition Flash</t>
+          <t>Model_SOMATOM Drive</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-13.2283</v>
+        <v>-41.8123</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -3350,11 +3323,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Drive</t>
+          <t>Model_SOMATOM Emotion 16</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>-47.8223</v>
+        <v>-45.6609</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -3372,11 +3345,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Emotion 16</t>
+          <t>Model_SOMATOM Force</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>-52.1735</v>
+        <v>-10.9442</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -3394,11 +3367,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Force</t>
+          <t>Model_SOMATOM Perspective</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>-13.7888</v>
+        <v>-9.9175</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -3416,11 +3389,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Perspective</t>
+          <t>Model_SOMATOM Scope</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>-12.7478</v>
+        <v>-10.9757</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -3438,14 +3411,14 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Scope</t>
+          <t>Model_SOMATOM go.Top</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-13.7751</v>
+        <v>113.8601</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>2.810777264241634e+49</v>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
@@ -3460,14 +3433,14 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Model_SOMATOM go.Top</t>
+          <t>Model_Scope</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>130.2981</v>
+        <v>-70.49550000000001</v>
       </c>
       <c r="C47" t="n">
-        <v>3.87037835553249e+56</v>
+        <v>0</v>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
@@ -3482,11 +3455,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Model_Scope</t>
+          <t>Model_Sensation 16</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>-80.0461</v>
+        <v>-29.0795</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -3504,14 +3477,14 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Model_Sensation 16</t>
+          <t>Model_Sensation 64</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-33.5737</v>
+        <v>-9.481999999999999</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
@@ -3526,11 +3499,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Model_Sensation 64</t>
+          <t>Model_Sensation Open</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-12.3246</v>
+        <v>-11.3951</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
@@ -3548,14 +3521,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Model_Sensation Open</t>
+          <t>Model_Spirit</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-14.2618</v>
+        <v>100.0617</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>2.859289574977098e+43</v>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
@@ -3570,14 +3543,14 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Model_Spirit</t>
+          <t>Model_Supria</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>120.0481</v>
+        <v>84.91030000000001</v>
       </c>
       <c r="C52" t="n">
-        <v>1.368410416321512e+52</v>
+        <v>7.517643574938535e+36</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
@@ -3592,14 +3565,14 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Model_Supria</t>
+          <t>Model_iCT 256</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>106.3247</v>
+        <v>-10.3286</v>
       </c>
       <c r="C53" t="n">
-        <v>1.500434470303972e+46</v>
+        <v>0</v>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
@@ -3614,42 +3587,20 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Model_iCT 256</t>
+          <t>Model_iCT SP</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-13.2114</v>
+        <v>176.5196</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>4.586562914514311e+76</v>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Model_iCT SP</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>205.8957</v>
-      </c>
-      <c r="C55" t="n">
-        <v>2.626468207671853e+89</v>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
@@ -3688,7 +3639,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1297</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="3">
@@ -3698,7 +3649,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5814</v>
+        <v>0.584</v>
       </c>
     </row>
     <row r="4">
@@ -3708,7 +3659,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5636</v>
+        <v>0.5661</v>
       </c>
     </row>
     <row r="5">
@@ -3718,7 +3669,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.5792</v>
+        <v>32.7138</v>
       </c>
     </row>
     <row r="6">
@@ -3729,7 +3680,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>3.1680e-196</t>
+          <t>9.4353e-193</t>
         </is>
       </c>
     </row>
@@ -3740,7 +3691,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19.9873</v>
+        <v>19.9457</v>
       </c>
     </row>
     <row r="8">
@@ -3750,7 +3701,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14.6877</v>
+        <v>14.6597</v>
       </c>
     </row>
     <row r="9">
@@ -3760,7 +3711,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11558.01</v>
+        <v>11268.24</v>
       </c>
     </row>
     <row r="10">
@@ -3770,7 +3721,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11837.08</v>
+        <v>11540.81</v>
       </c>
     </row>
   </sheetData>
@@ -3806,7 +3757,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1297</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="3">
@@ -3816,7 +3767,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>319</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4">
@@ -3826,7 +3777,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.718</v>
+        <v>0.7221</v>
       </c>
     </row>
     <row r="5">
@@ -3836,7 +3787,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6868</v>
+        <v>0.6881</v>
       </c>
     </row>
     <row r="6">
@@ -3846,7 +3797,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7494</v>
+        <v>0.7531</v>
       </c>
     </row>
     <row r="7">
@@ -3856,7 +3807,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.283</v>
+        <v>6.3538</v>
       </c>
     </row>
     <row r="8">
@@ -3867,7 +3818,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6.1556e-01</t>
+          <t>6.0767e-01</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3841,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1713</v>
+        <v>0.1755</v>
       </c>
     </row>
     <row r="11">
@@ -3900,7 +3851,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.162</v>
+        <v>0.1625</v>
       </c>
     </row>
     <row r="12">
@@ -3910,7 +3861,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1396.34</v>
+        <v>1364.49</v>
       </c>
     </row>
     <row r="13">
@@ -3920,7 +3871,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1675.4</v>
+        <v>1637.06</v>
       </c>
     </row>
     <row r="14">
@@ -3991,19 +3942,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>104.0081</v>
+        <v>104.0703</v>
       </c>
       <c r="C2" t="n">
-        <v>102.3503</v>
+        <v>102.3779</v>
       </c>
       <c r="D2" t="n">
-        <v>105.666</v>
+        <v>105.7627</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8451</v>
+        <v>0.8627</v>
       </c>
       <c r="F2" t="n">
-        <v>123.076</v>
+        <v>120.6393</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -4018,23 +3969,23 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.4676</v>
+        <v>44.1838</v>
       </c>
       <c r="C3" t="n">
-        <v>42.119</v>
+        <v>41.7951</v>
       </c>
       <c r="D3" t="n">
-        <v>46.8162</v>
+        <v>46.5724</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1972</v>
+        <v>1.2175</v>
       </c>
       <c r="F3" t="n">
-        <v>37.1442</v>
+        <v>36.2892</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3.7141e-206</t>
+          <t>4.4664e-198</t>
         </is>
       </c>
     </row>
@@ -4045,23 +3996,23 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-4.1557</v>
+        <v>-4.2844</v>
       </c>
       <c r="C4" t="n">
-        <v>-5.33</v>
+        <v>-5.4787</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.9814</v>
+        <v>-3.0901</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5986</v>
+        <v>0.6088</v>
       </c>
       <c r="F4" t="n">
-        <v>-6.9426</v>
+        <v>-7.038</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6.0738e-12</t>
+          <t>3.1922e-12</t>
         </is>
       </c>
     </row>
@@ -4128,26 +4079,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.1557</v>
+        <v>-1.1443</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3148</v>
+        <v>0.3185</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2623</v>
+        <v>0.2647</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3779</v>
+        <v>0.3832</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.0944</v>
       </c>
       <c r="G2" t="n">
-        <v>-12.3999</v>
+        <v>-12.1262</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2.6171e-35</t>
+          <t>7.6760e-34</t>
         </is>
       </c>
     </row>
@@ -4158,26 +4109,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0049</v>
+        <v>0.0059</v>
       </c>
       <c r="C3" t="n">
-        <v>1.005</v>
+        <v>1.0059</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7773</v>
+        <v>0.7763</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2993</v>
+        <v>1.3033</v>
       </c>
       <c r="F3" t="n">
-        <v>0.131</v>
+        <v>0.1322</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0378</v>
+        <v>0.0443</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>9.6987e-01</t>
+          <t>9.6466e-01</t>
         </is>
       </c>
     </row>
@@ -4188,26 +4139,26 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3618</v>
+        <v>0.3652</v>
       </c>
       <c r="C4" t="n">
-        <v>1.436</v>
+        <v>1.4407</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2468</v>
+        <v>1.2494</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6538</v>
+        <v>1.6613</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0721</v>
+        <v>0.0727</v>
       </c>
       <c r="G4" t="n">
-        <v>5.0209</v>
+        <v>5.0239</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5.1418e-07</t>
+          <t>5.0626e-07</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4195,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1297</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="3">
@@ -4254,7 +4205,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5183</v>
+        <v>0.5139</v>
       </c>
     </row>
     <row r="4">
@@ -4264,7 +4215,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.5132</v>
       </c>
     </row>
     <row r="5">
@@ -4274,7 +4225,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>696.1707</v>
+        <v>667.218</v>
       </c>
     </row>
     <row r="6">
@@ -4285,7 +4236,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5.6777e-206</t>
+          <t>1.9777e-198</t>
         </is>
       </c>
     </row>
@@ -4296,7 +4247,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21.4418</v>
+        <v>21.5585</v>
       </c>
     </row>
     <row r="8">
@@ -4306,7 +4257,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15.8795</v>
+        <v>15.9654</v>
       </c>
     </row>
     <row r="9">
@@ -4316,7 +4267,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11638.23</v>
+        <v>11364.96</v>
       </c>
     </row>
     <row r="10">
@@ -4326,7 +4277,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11653.73</v>
+        <v>11380.39</v>
       </c>
     </row>
   </sheetData>
@@ -4362,7 +4313,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1297</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="3">
@@ -4372,7 +4323,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>319</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4">
@@ -4382,7 +4333,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.614</v>
+        <v>0.6146</v>
       </c>
     </row>
     <row r="5">
@@ -4392,7 +4343,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5737</v>
+        <v>0.5783</v>
       </c>
     </row>
     <row r="6">
@@ -4402,7 +4353,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6526</v>
+        <v>0.6522</v>
       </c>
     </row>
     <row r="7">
@@ -4412,7 +4363,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25.6266</v>
+        <v>25.0559</v>
       </c>
     </row>
     <row r="8">
@@ -4423,7 +4374,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.2160e-03</t>
+          <t>1.5210e-03</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4397,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.0314</v>
+        <v>0.0321</v>
       </c>
     </row>
     <row r="11">
@@ -4456,7 +4407,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1806</v>
+        <v>0.1816</v>
       </c>
     </row>
     <row r="12">
@@ -4466,7 +4417,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1425.39</v>
+        <v>1396.11</v>
       </c>
     </row>
     <row r="13">
@@ -4476,7 +4427,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1440.9</v>
+        <v>1411.54</v>
       </c>
     </row>
     <row r="14">
@@ -4547,19 +4498,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>104.6503</v>
+        <v>104.728</v>
       </c>
       <c r="C2" t="n">
-        <v>103.0173</v>
+        <v>103.0639</v>
       </c>
       <c r="D2" t="n">
-        <v>106.2833</v>
+        <v>106.392</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8324</v>
+        <v>0.8482</v>
       </c>
       <c r="F2" t="n">
-        <v>125.7208</v>
+        <v>123.4709</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -4574,23 +4525,23 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>43.1842</v>
+        <v>42.8777</v>
       </c>
       <c r="C3" t="n">
-        <v>40.8439</v>
+        <v>40.5005</v>
       </c>
       <c r="D3" t="n">
-        <v>45.5246</v>
+        <v>45.2549</v>
       </c>
       <c r="E3" t="n">
-        <v>1.193</v>
+        <v>1.2117</v>
       </c>
       <c r="F3" t="n">
-        <v>36.1991</v>
+        <v>35.3858</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1.4794e-198</t>
+          <t>6.7884e-191</t>
         </is>
       </c>
     </row>
@@ -4601,23 +4552,23 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-4.3406</v>
+        <v>-4.527</v>
       </c>
       <c r="C4" t="n">
-        <v>-5.5087</v>
+        <v>-5.7111</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.1724</v>
+        <v>-3.3429</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5954</v>
+        <v>0.6035</v>
       </c>
       <c r="F4" t="n">
-        <v>-7.2898</v>
+        <v>-7.5006</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>5.3976e-13</t>
+          <t>1.1962e-13</t>
         </is>
       </c>
     </row>
@@ -4628,23 +4579,23 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-5.306</v>
+        <v>-9.0405</v>
       </c>
       <c r="C5" t="n">
-        <v>-14.1149</v>
+        <v>-18.4696</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5029</v>
+        <v>0.3887</v>
       </c>
       <c r="E5" t="n">
-        <v>4.4902</v>
+        <v>4.8062</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1817</v>
+        <v>-1.881</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.3755e-01</t>
+          <t>6.0205e-02</t>
         </is>
       </c>
     </row>
@@ -4655,23 +4606,23 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-2.1333</v>
+        <v>-2.8065</v>
       </c>
       <c r="C6" t="n">
-        <v>-3.9438</v>
+        <v>-4.672</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3229</v>
+        <v>-0.9411</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9228</v>
+        <v>0.9509</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.3117</v>
+        <v>-2.9515</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.0950e-02</t>
+          <t>3.2207e-03</t>
         </is>
       </c>
     </row>
@@ -4682,23 +4633,23 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.6146</v>
+        <v>1.3033</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2918</v>
+        <v>-0.0424</v>
       </c>
       <c r="D7" t="n">
-        <v>2.9374</v>
+        <v>2.649</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6743</v>
+        <v>0.6859</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3945</v>
+        <v>1.9</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.6785e-02</t>
+          <t>5.7657e-02</t>
         </is>
       </c>
     </row>
@@ -4709,23 +4660,23 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8077</v>
+        <v>0.7759</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.3898</v>
+        <v>-0.4415</v>
       </c>
       <c r="D8" t="n">
-        <v>2.0052</v>
+        <v>1.9934</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6104000000000001</v>
+        <v>0.6206</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3232</v>
+        <v>1.2503</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.8602e-01</t>
+          <t>2.1141e-01</t>
         </is>
       </c>
     </row>
@@ -4736,23 +4687,23 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.934100000000001</v>
+        <v>13.5949</v>
       </c>
       <c r="C9" t="n">
-        <v>1.4916</v>
+        <v>4.5157</v>
       </c>
       <c r="D9" t="n">
-        <v>18.3765</v>
+        <v>22.6741</v>
       </c>
       <c r="E9" t="n">
-        <v>4.3034</v>
+        <v>4.6279</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3084</v>
+        <v>2.9376</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.1134e-02</t>
+          <t>3.3678e-03</t>
         </is>
       </c>
     </row>
@@ -4819,26 +4770,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-1.2643</v>
+        <v>-1.2522</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2824</v>
+        <v>0.2859</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2327</v>
+        <v>0.235</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3428</v>
+        <v>0.3478</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0988</v>
+        <v>0.1001</v>
       </c>
       <c r="G2" t="n">
-        <v>-12.7967</v>
+        <v>-12.5137</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1.7113e-37</t>
+          <t>6.2821e-36</t>
         </is>
       </c>
     </row>
@@ -4849,26 +4800,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1255</v>
+        <v>0.1217</v>
       </c>
       <c r="C3" t="n">
-        <v>1.1337</v>
+        <v>1.1294</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8666</v>
+        <v>0.8607</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4832</v>
+        <v>1.482</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1371</v>
+        <v>0.1386</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9155</v>
+        <v>0.8781</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.5990e-01</t>
+          <t>3.7990e-01</t>
         </is>
       </c>
     </row>
@@ -4879,26 +4830,26 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4096</v>
+        <v>0.4137</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5063</v>
+        <v>1.5125</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3017</v>
+        <v>1.3054</v>
       </c>
       <c r="E4" t="n">
-        <v>1.743</v>
+        <v>1.7524</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0745</v>
+        <v>0.0751</v>
       </c>
       <c r="G4" t="n">
-        <v>5.4994</v>
+        <v>5.5075</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.8119e-08</t>
+          <t>3.6405e-08</t>
         </is>
       </c>
     </row>
@@ -4909,26 +4860,26 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5991</v>
+        <v>0.7491</v>
       </c>
       <c r="C5" t="n">
-        <v>1.8205</v>
+        <v>2.1152</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5638</v>
+        <v>0.6113</v>
       </c>
       <c r="E5" t="n">
-        <v>5.8786</v>
+        <v>7.3184</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5981</v>
+        <v>0.6333</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0018</v>
+        <v>1.1829</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.1645e-01</t>
+          <t>2.3685e-01</t>
         </is>
       </c>
     </row>
@@ -4939,26 +4890,26 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.2958</v>
+        <v>0.3267</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3442</v>
+        <v>1.3864</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0906</v>
+        <v>1.1191</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6568</v>
+        <v>1.7176</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1067</v>
+        <v>0.1093</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7726</v>
+        <v>2.9898</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5.5612e-03</t>
+          <t>2.7913e-03</t>
         </is>
       </c>
     </row>
@@ -4969,26 +4920,26 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.1241</v>
+        <v>-0.1392</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8833</v>
+        <v>0.87</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7592</v>
+        <v>0.7441</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0277</v>
+        <v>1.0173</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0772</v>
+        <v>0.0798</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.6069</v>
+        <v>-1.7447</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.0809e-01</t>
+          <t>8.1030e-02</t>
         </is>
       </c>
     </row>
@@ -4999,26 +4950,26 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.0411</v>
+        <v>-0.0423</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9597</v>
+        <v>0.9585</v>
       </c>
       <c r="D8" t="n">
-        <v>0.804</v>
+        <v>0.7978</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1457</v>
+        <v>1.1517</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4549</v>
+        <v>-0.4521</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6.4915e-01</t>
+          <t>6.5116e-01</t>
         </is>
       </c>
     </row>
@@ -5029,26 +4980,26 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.9719</v>
+        <v>-1.1159</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3784</v>
+        <v>0.3276</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1247</v>
+        <v>0.1007</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1479</v>
+        <v>1.0662</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5663</v>
+        <v>0.602</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7163</v>
+        <v>-1.8535</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8.6104e-02</t>
+          <t>6.3816e-02</t>
         </is>
       </c>
     </row>
@@ -5085,7 +5036,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1297</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="3">
@@ -5095,7 +5046,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5455</v>
+        <v>0.5437</v>
       </c>
     </row>
     <row r="4">
@@ -5105,7 +5056,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.543</v>
+        <v>0.5411</v>
       </c>
     </row>
     <row r="5">
@@ -5115,7 +5066,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>220.9896</v>
+        <v>213.9411</v>
       </c>
     </row>
     <row r="6">
@@ -5126,7 +5077,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.3924e-215</t>
+          <t>4.7165e-209</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5088,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20.8283</v>
+        <v>20.8889</v>
       </c>
     </row>
     <row r="8">
@@ -5147,7 +5098,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15.4551</v>
+        <v>15.4942</v>
       </c>
     </row>
     <row r="9">
@@ -5157,7 +5108,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11572.92</v>
+        <v>11295.14</v>
       </c>
     </row>
     <row r="10">
@@ -5167,7 +5118,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11614.27</v>
+        <v>11336.28</v>
       </c>
     </row>
   </sheetData>
@@ -5203,7 +5154,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1297</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="3">
@@ -5213,7 +5164,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>319</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4">
@@ -5223,7 +5174,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6546</v>
+        <v>0.655</v>
       </c>
     </row>
     <row r="5">
@@ -5233,7 +5184,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6192</v>
+        <v>0.6211</v>
       </c>
     </row>
     <row r="6">
@@ -5243,7 +5194,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6893</v>
+        <v>0.6911</v>
       </c>
     </row>
     <row r="7">
@@ -5253,7 +5204,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11.4673</v>
+        <v>13.6865</v>
       </c>
     </row>
     <row r="8">
@@ -5264,7 +5215,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.7660e-01</t>
+          <t>9.0313e-02</t>
         </is>
       </c>
     </row>
@@ -5287,7 +5238,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.07920000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -5297,7 +5248,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1748</v>
+        <v>0.1754</v>
       </c>
     </row>
     <row r="12">
@@ -5307,7 +5258,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1395.6</v>
+        <v>1364.37</v>
       </c>
     </row>
     <row r="13">
@@ -5317,7 +5268,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1436.95</v>
+        <v>1405.51</v>
       </c>
     </row>
     <row r="14">
